--- a/assets/docs/lop5/Tieng Anh - Lop 5.xlsx
+++ b/assets/docs/lop5/Tieng Anh - Lop 5.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.1 CB2c: Pupils look at the English 5 e-book on the TV, point to the Unit and Lesson sections and say the name of the part they will learn.</t>
+          <t>Digital Competence: 1.1CB2a: Identifying information needs regarding the structure of soft books/e-books (Students recognize the need to use digital versions for self-study and identify the basic components of the e-book interface).</t>
         </is>
       </c>
     </row>
@@ -1496,8 +1496,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 4 Our free-time activities, the teacher plays the audio file of the conversation and shows pictures with key words; pupils listen the first time for the general idea
-Digital competence Domain 3 (Basic, level 2): Each group makes a page about the group's free-time activities: choose activity icons, write how often and write two sentences in English
+          <t>Digital Competence (4.3CB1a): Avoiding health risks (moving according to a video). Pupils perform physical movements following a "Brain Break" video to relax their muscles and eyes after using digital devices.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1536,8 +1535,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 4 Our free-time activities, the teacher opens an interactive exercise: listen and choose the picture and match free-time activities with how often they are done
-Digital competence Domain 2 (Basic, level 2): The teacher records a few pairs asking and answering about free-time activities and plays them to the class; pupils comment using the criteria: full sentences, clear pronunciation
+          <t>Core Competence (1.3CB1b): Arrange information (vocabulary) in correct sentence structures, specifically using the patterns: I like + V-ing and Do you + V...?
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1576,8 +1574,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 3 My foreign friends, the teacher plays the audio file of a conversation describing friends' personalities and shows pictures with key words
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to match personality words with example situations and fill in the missing words in sentences
+          <t>Competency 1.1CB1c: Search for and identify words containing the sounds /air/ and /ear/ within the context of free-time activities (e.g., near, hear, chair, pair).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1810,8 +1807,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 My future job, the teacher shows a set of job pictures with model audio; pupils listen and match the job names with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of dream jobs; each pair asks and answers in English and then reads out the answers for the teacher to tick
+          <t>Competency 1.1CB1c: Search for and identify words containing the sounds /air/ and /ear/ within the context of free-time activities (e.g., near, hear, chair, pair).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2782,8 +2778,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Let's sing activity of Unit 9 “Our outdoor activities”, the teacher plays the song What did you do? with scrolling lyrics on the screen
-Digital competence Domain 2 (Basic, level 2): In the Read and write activity, the teacher shows a text with blanks on the screen; groups discuss and then come up to fill in the blanks
+          <t>Digital Competence (3.2CB2a): Identify simple ways to adjust and customize the digital environment: Adjust the itinerary/plan of the trip (e.g., reordering activities, selecting activities) on a simple digital interface (like a slide or a digital list) to suit personal needs.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2860,8 +2855,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 8 In our classroom, the teacher shows a classroom picture with key words and plays the audio file; pupils listen the first time for the general idea
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen, drag the things to the right positions and fill in the missing location words
+          <t>Digital Competence (1.1CB2c): Identify information needs; search for data, information, and content.(Specifically: Pupils realize the need to check pronunciation/stress and can use (or observe the use of) a simple online dictionary to find the stress pattern of new words).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4719,9 +4713,7 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Warm-up of Unit 15 “Our health”, the teacher shows a table of vocabulary about health and advice on the screen for pupils to look up when they forget a word
-Digital competence Domain 2 (Basic, level 2): In the Conversation making activity, the teacher shows a model conversation frame on the screen; pairs build their own conversations following the frame and present them
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
